--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -701,7 +701,7 @@
 </t>
   </si>
   <si>
-    <t>Security Labels applied to this resource</t>
+    <t>Säkerhetsetiketter som FHIR-EI tillämpar per syfte, t.ex. NOPAT</t>
   </si>
   <si>
     <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
@@ -8160,7 +8160,7 @@
         <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>77</v>
